--- a/site/UKG-Ready-Zendesk-Integration-Guide/headings.xlsx
+++ b/site/UKG-Ready-Zendesk-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,6 +548,138 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01KX55DXMWEN1HY3ZF9PJYYQHW</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/UKG-Ready-Zendesk-Integration-Guide/#h_01KX55DXMWEN1HY3ZF9PJYYQHW</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Features</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01KX55H7MQ8J7D8ZSFXEMNG03Q</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/UKG-Ready-Zendesk-Integration-Guide/#h_01KX55H7MQ8J7D8ZSFXEMNG03Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Service Desk Bridge</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/UKG-Ready-Zendesk-Integration-Guide/#h_01KW1TH82EGE4EW275DJSB2X28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01KX55KZG2PA5N986S4ZG7KW6R</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/UKG-Ready-Zendesk-Integration-Guide/#h_01KX55KZG2PA5N986S4ZG7KW6R</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Application Settings</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KX55QJZAW6R5CD1WMG5T6PZ9</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/UKG-Ready-Zendesk-Integration-Guide/#h_01KX55QJZAW6R5CD1WMG5T6PZ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Advanced settings</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KX564VSGVD3M22459CP8GRN0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/UKG-Ready-Zendesk-Integration-Guide/#h_01KX564VSGVD3M22459CP8GRN0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
